--- a/upload/Moment Atualizado.xlsx
+++ b/upload/Moment Atualizado.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>UNIDADE</t>
   </si>
@@ -33,6 +33,9 @@
     <t>TIPOLOGIA</t>
   </si>
   <si>
+    <t>STATUS</t>
+  </si>
+  <si>
     <t>VALOR</t>
   </si>
   <si>
@@ -43,6 +46,9 @@
   </si>
   <si>
     <t xml:space="preserve">3 quartos (1 suíte + 2 semissuítes)</t>
+  </si>
+  <si>
+    <t>Disponível</t>
   </si>
   <si>
     <t xml:space="preserve">89,34 m²</t>
@@ -1027,8 +1033,8 @@
     <col bestFit="1" min="3" max="3" style="1" width="8.00390625"/>
     <col bestFit="1" min="4" max="4" style="1" width="12.8515625"/>
     <col bestFit="1" min="5" max="5" style="1" width="34.57421875"/>
-    <col bestFit="1" min="6" max="6" style="1" width="16.28125"/>
-    <col min="7" max="16384" style="1" width="10.28125"/>
+    <col bestFit="1" min="6" max="7" style="1" width="16.28125"/>
+    <col min="8" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25">
@@ -1050,1452 +1056,1594 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" ht="23.25">
       <c r="A2" s="1">
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2">
         <v>2240814.8399999999</v>
       </c>
-      <c r="G2" s="1"/>
     </row>
     <row r="3" ht="23.25">
       <c r="A3" s="1">
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2">
         <v>1699023.48</v>
       </c>
-      <c r="G3" s="1"/>
     </row>
     <row r="4" ht="23.25">
       <c r="A4" s="1">
         <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2">
         <v>1647260.4099999999</v>
       </c>
-      <c r="G4" s="1"/>
     </row>
     <row r="5" ht="23.25">
       <c r="A5" s="1">
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2">
         <v>1680577.25</v>
       </c>
-      <c r="G5" s="1"/>
     </row>
     <row r="6" ht="23.25">
       <c r="A6" s="1">
         <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
         <v>1617936.55</v>
       </c>
-      <c r="G6" s="1"/>
     </row>
     <row r="7" ht="23.25">
       <c r="A7" s="1">
         <v>106</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="2">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
         <v>2065538.3700000001</v>
       </c>
-      <c r="G7" s="1"/>
     </row>
     <row r="8" ht="23.25">
       <c r="A8" s="1">
         <v>107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="2">
+        <v>28</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2">
         <v>2065538.3700000001</v>
       </c>
-      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="23.25">
       <c r="A9" s="1">
         <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2">
+        <v>31</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
         <v>1647633.6000000001</v>
       </c>
-      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="23.25">
       <c r="A10" s="1">
         <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" ht="23.25">
       <c r="A11" s="1">
         <v>110</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1">
         <v>2</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="2">
+        <v>38</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
         <v>1643309.45</v>
       </c>
-      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="23.25">
       <c r="A12" s="1">
         <v>111</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="2">
+        <v>41</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
         <v>1622902.73</v>
       </c>
-      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="23.25">
       <c r="A13" s="1">
         <v>112</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="2">
+        <v>44</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
         <v>2191534.3599999999</v>
       </c>
-      <c r="G13" s="1"/>
     </row>
     <row r="14" ht="23.25">
       <c r="A14" s="1">
         <v>201</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="2">
+        <v>46</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2">
         <v>2307020.4399999999</v>
       </c>
-      <c r="G14" s="1"/>
     </row>
     <row r="15" ht="23.25">
       <c r="A15" s="1">
         <v>202</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="2">
+        <v>48</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2">
         <v>1749995.05</v>
       </c>
-      <c r="G15" s="1"/>
     </row>
     <row r="16" ht="23.25">
       <c r="A16" s="1">
         <v>203</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="2">
+        <v>50</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2">
         <v>1696678.02</v>
       </c>
-      <c r="G16" s="1"/>
     </row>
     <row r="17" ht="23.25">
       <c r="A17" s="1">
         <v>204</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="2">
+        <v>52</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2">
         <v>1730993.8600000001</v>
       </c>
-      <c r="G17" s="1"/>
     </row>
     <row r="18" ht="23.25">
       <c r="A18" s="1">
         <v>205</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="2">
+        <v>54</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2">
         <v>1666474.49</v>
       </c>
-      <c r="G18" s="1"/>
     </row>
     <row r="19" ht="23.25">
       <c r="A19" s="1">
         <v>206</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="2">
+        <v>56</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2">
         <v>2126485.3300000001</v>
       </c>
-      <c r="G19" s="1"/>
     </row>
     <row r="20" ht="23.25">
       <c r="A20" s="1">
         <v>207</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="2">
+        <v>58</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2">
         <v>2126485.3300000001</v>
       </c>
-      <c r="G20" s="1"/>
     </row>
     <row r="21" ht="23.25">
       <c r="A21" s="1">
         <v>208</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="2">
+        <v>60</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="2">
         <v>1697061.97</v>
       </c>
-      <c r="G21" s="1"/>
     </row>
     <row r="22" ht="23.25">
       <c r="A22" s="1">
         <v>209</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="2">
+        <v>62</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2">
         <v>1665542.1499999999</v>
       </c>
-      <c r="G22" s="1"/>
     </row>
     <row r="23" ht="23.25">
       <c r="A23" s="1">
         <v>210</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="2">
+        <v>64</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2">
         <v>1692607.7</v>
       </c>
-      <c r="G23" s="1"/>
     </row>
     <row r="24" ht="23.25">
       <c r="A24" s="1">
         <v>211</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="2">
+        <v>66</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2">
         <v>1671590.1399999999</v>
       </c>
-      <c r="G24" s="1"/>
     </row>
     <row r="25" ht="23.25">
       <c r="A25" s="1">
         <v>212</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C25" s="1">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" s="2">
+        <v>68</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2">
         <v>2256269.21</v>
       </c>
-      <c r="G25" s="1"/>
     </row>
     <row r="26" ht="23.25">
       <c r="A26" s="1">
         <v>301</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="2">
+        <v>70</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2">
         <v>2329751.04</v>
       </c>
-      <c r="G26" s="1"/>
     </row>
     <row r="27" ht="23.25">
       <c r="A27" s="1">
         <v>302</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" ht="23.25">
       <c r="A28" s="1">
         <v>303</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" s="2">
+        <v>73</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
         <v>1699538.3799999999</v>
       </c>
-      <c r="G28" s="1"/>
     </row>
     <row r="29" ht="23.25">
       <c r="A29" s="1">
         <v>304</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="2">
+        <v>75</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2">
         <v>1748304.53</v>
       </c>
-      <c r="G29" s="1"/>
     </row>
     <row r="30" ht="23.25">
       <c r="A30" s="1">
         <v>305</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="2">
+        <v>77</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2">
         <v>1683139.8799999999</v>
       </c>
-      <c r="G30" s="1"/>
     </row>
     <row r="31" ht="23.25">
       <c r="A31" s="1">
         <v>306</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="2">
+        <v>79</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2">
         <v>2147411.3900000001</v>
       </c>
-      <c r="G31" s="1"/>
     </row>
     <row r="32" ht="23.25">
       <c r="A32" s="1">
         <v>307</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C32" s="1">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="2">
+        <v>81</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2">
         <v>2147411.3900000001</v>
       </c>
-      <c r="G32" s="1"/>
     </row>
     <row r="33" ht="23.25">
       <c r="A33" s="1">
         <v>308</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C33" s="1">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="2">
+        <v>83</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2">
         <v>1714032.76</v>
       </c>
-      <c r="G33" s="1"/>
     </row>
     <row r="34" ht="23.25">
       <c r="A34" s="1">
         <v>309</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" s="2">
+        <v>85</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2">
         <v>1682197.8300000001</v>
       </c>
-      <c r="G34" s="1"/>
     </row>
     <row r="35" ht="23.25">
       <c r="A35" s="1">
         <v>310</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C35" s="1">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="2">
+        <v>87</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2">
         <v>1709534.3899999999</v>
       </c>
-      <c r="G35" s="1"/>
     </row>
     <row r="36" ht="23.25">
       <c r="A36" s="1">
         <v>311</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" s="2">
+        <v>89</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2">
         <v>1688306.1000000001</v>
       </c>
-      <c r="G36" s="1"/>
     </row>
     <row r="37" ht="23.25">
       <c r="A37" s="1">
         <v>312</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C37" s="1">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F37" s="2">
+        <v>91</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2">
         <v>2278494.8799999999</v>
       </c>
-      <c r="G37" s="1"/>
     </row>
     <row r="38" ht="23.25">
       <c r="A38" s="1">
         <v>401</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G38" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="39" ht="23.25">
       <c r="A39" s="1">
         <v>402</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C39" s="1">
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="40" ht="23.25">
       <c r="A40" s="1">
         <v>403</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F40" s="2">
+        <v>94</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2">
         <v>1716533.73</v>
       </c>
-      <c r="G40" s="1"/>
     </row>
     <row r="41" ht="23.25">
       <c r="A41" s="1">
         <v>404</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C41" s="1">
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" s="2">
+        <v>96</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2">
         <v>1765787.1799999999</v>
       </c>
-      <c r="G41" s="1"/>
     </row>
     <row r="42" ht="23.25">
       <c r="A42" s="1">
         <v>405</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C42" s="1">
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F42" s="2">
+        <v>98</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2">
         <v>1699970.8799999999</v>
       </c>
-      <c r="G42" s="1"/>
     </row>
     <row r="43" ht="23.25">
       <c r="A43" s="1">
         <v>406</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C43" s="1">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F43" s="2">
+        <v>100</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2">
         <v>2168545.0899999999</v>
       </c>
-      <c r="G43" s="1"/>
     </row>
     <row r="44" ht="23.25">
       <c r="A44" s="1">
         <v>407</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="1">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F44" s="2">
+        <v>102</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2">
         <v>2168545.0899999999</v>
       </c>
-      <c r="G44" s="1"/>
     </row>
     <row r="45" ht="23.25">
       <c r="A45" s="1">
         <v>408</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C45" s="1">
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F45" s="2">
+        <v>104</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2">
         <v>1731173.48</v>
       </c>
-      <c r="G45" s="1"/>
     </row>
     <row r="46" ht="23.25">
       <c r="A46" s="1">
         <v>409</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C46" s="1">
         <v>2</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F46" s="2">
+        <v>106</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2">
         <v>1699019.1699999999</v>
       </c>
-      <c r="G46" s="1"/>
     </row>
     <row r="47" ht="23.25">
       <c r="A47" s="1">
         <v>410</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F47" s="2">
+        <v>108</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2">
         <v>1726629.96</v>
       </c>
-      <c r="G47" s="1"/>
     </row>
     <row r="48" ht="23.25">
       <c r="A48" s="1">
         <v>411</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F48" s="2">
+        <v>110</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2">
         <v>1705188.74</v>
       </c>
-      <c r="G48" s="1"/>
     </row>
     <row r="49" ht="23.25">
       <c r="A49" s="1">
         <v>412</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C49" s="1">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F49" s="2">
+        <v>112</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="2">
         <v>2300943.4700000002</v>
       </c>
-      <c r="G49" s="1"/>
     </row>
     <row r="50" ht="23.25">
       <c r="A50" s="1">
         <v>501</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" s="1">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F50" s="2">
+        <v>114</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2">
         <v>2375896.2200000002</v>
       </c>
-      <c r="G50" s="1"/>
     </row>
     <row r="51" ht="23.25">
       <c r="A51" s="1">
         <v>502</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C51" s="1">
         <v>2</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F51" s="2">
+        <v>116</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2">
         <v>1820001.05</v>
       </c>
-      <c r="G51" s="1"/>
     </row>
     <row r="52" ht="23.25">
       <c r="A52" s="1">
         <v>503</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C52" s="1">
         <v>2</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F52" s="2">
+        <v>118</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2">
         <v>1733698.6599999999</v>
       </c>
-      <c r="G52" s="1"/>
     </row>
     <row r="53" ht="23.25">
       <c r="A53" s="1">
         <v>504</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C53" s="1">
         <v>2</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F53" s="2">
+        <v>120</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2">
         <v>1800424.5700000001</v>
       </c>
-      <c r="G53" s="1"/>
     </row>
     <row r="54" ht="23.25">
       <c r="A54" s="1">
         <v>505</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C54" s="1">
         <v>2</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F54" s="2">
+        <v>122</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="2">
         <v>1716970.76</v>
       </c>
-      <c r="G54" s="1"/>
     </row>
     <row r="55" ht="23.25">
       <c r="A55" s="1">
         <v>506</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C55" s="1">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F55" s="2">
+        <v>124</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2">
         <v>2189891.6899999999</v>
       </c>
-      <c r="G55" s="1"/>
     </row>
     <row r="56" ht="23.25">
       <c r="A56" s="1">
         <v>507</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F56" s="2">
+        <v>126</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="2">
         <v>2189891.6899999999</v>
       </c>
-      <c r="G56" s="1"/>
     </row>
     <row r="57" ht="23.25">
       <c r="A57" s="1">
         <v>508</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F57" s="2">
+        <v>128</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="2">
         <v>1765464.5600000001</v>
       </c>
-      <c r="G57" s="1"/>
     </row>
     <row r="58" ht="23.25">
       <c r="A58" s="1">
         <v>509</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C58" s="1">
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F58" s="2">
+        <v>130</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2">
         <v>1716009.3400000001</v>
       </c>
-      <c r="G58" s="1"/>
     </row>
     <row r="59" ht="23.25">
       <c r="A59" s="1">
         <v>510</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C59" s="1">
         <v>2</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F59" s="2">
+        <v>132</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="2">
         <v>1743895.3999999999</v>
       </c>
-      <c r="G59" s="1"/>
     </row>
     <row r="60" ht="23.25">
       <c r="A60" s="1">
         <v>511</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C60" s="1">
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F60" s="2">
+        <v>134</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="2">
         <v>1722241.27</v>
       </c>
-      <c r="G60" s="1"/>
     </row>
     <row r="61" ht="23.25">
       <c r="A61" s="1">
         <v>512</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C61" s="1">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F61" s="2">
+        <v>136</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="2">
         <v>2323616.04</v>
       </c>
-      <c r="G61" s="1"/>
     </row>
     <row r="62" ht="23.25">
       <c r="A62" s="1">
         <v>601</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C62" s="1">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F62" s="2">
+        <v>139</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="2">
         <v>2375896.2200000002</v>
       </c>
-      <c r="G62" s="1"/>
     </row>
     <row r="63" ht="23.25">
       <c r="A63" s="1">
         <v>602</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C63" s="1">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F63" s="2">
+        <v>142</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="2">
         <v>1836980.47</v>
       </c>
-      <c r="G63" s="1"/>
     </row>
     <row r="64" ht="23.25">
       <c r="A64" s="1">
         <v>603</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F64" s="2">
+        <v>144</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="2">
         <v>1750539.3799999999</v>
       </c>
-      <c r="G64" s="1"/>
     </row>
     <row r="65">
       <c r="A65" s="1">
         <v>604</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C65" s="1">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F65" s="2">
+        <v>147</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="2">
         <v>2915961.5299999998</v>
       </c>
-      <c r="G65" s="1"/>
     </row>
     <row r="66">
       <c r="A66" s="1">
         <v>605</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C66" s="1">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F66" s="2">
+        <v>150</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="2">
         <v>2937899.5899999999</v>
       </c>
-      <c r="G66" s="1"/>
     </row>
     <row r="67">
       <c r="A67" s="1">
         <v>606</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C67" s="1">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F67" s="2">
+        <v>153</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="2">
         <v>3351550.1699999999</v>
       </c>
-      <c r="G67" s="1"/>
     </row>
     <row r="68">
       <c r="A68" s="1">
         <v>607</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F68" s="2">
+        <v>156</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="2">
         <v>3354389.1800000002</v>
       </c>
-      <c r="G68" s="1"/>
     </row>
     <row r="69">
       <c r="A69" s="1">
         <v>608</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C69" s="1">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F69" s="2">
+        <v>159</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="2">
         <v>2993441.5899999999</v>
       </c>
-      <c r="G69" s="1"/>
     </row>
     <row r="70" ht="14.25">
       <c r="A70" s="1">
         <v>609</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C70" s="1">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F70" s="2">
+        <v>162</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="2">
         <v>2726253.3700000001</v>
       </c>
     </row>
@@ -2504,18 +2652,21 @@
         <v>610</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C71" s="1">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F71" s="2">
+        <v>165</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="2">
         <v>2697824.1600000001</v>
       </c>
     </row>
@@ -2524,18 +2675,21 @@
         <v>611</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C72" s="1">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F72" s="2">
+        <v>34</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="2">
         <v>2652046.8199999998</v>
       </c>
     </row>
@@ -2544,18 +2698,21 @@
         <v>612</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C73" s="1">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F73" s="2">
+        <v>92</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="2">
         <v>4156307.7200000002</v>
       </c>
     </row>
